--- a/Outcome/Appendix/figure_data/fig3.xlsx
+++ b/Outcome/Appendix/figure_data/fig3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">AgeGroup</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">1-3</t>
@@ -139,9 +136,6 @@
     <t xml:space="preserve">Leptospirosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Malaria</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cholera</t>
   </si>
   <si>
@@ -149,6 +143,9 @@
   </si>
   <si>
     <t xml:space="preserve">Other tetanus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaria</t>
   </si>
   <si>
     <t xml:space="preserve">HDV</t>
@@ -671,16 +668,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -691,16 +688,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -711,16 +708,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -731,19 +728,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -751,19 +748,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -771,16 +768,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -791,139 +788,139 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
-      </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -931,119 +928,119 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>22</v>
       </c>
-      <c r="B26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
         <v>22</v>
       </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
-      </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -1051,59 +1048,59 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -1111,19 +1108,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -1131,19 +1128,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -1154,16 +1151,16 @@
         <v>25</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -1174,19 +1171,19 @@
         <v>25</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -1194,16 +1191,16 @@
         <v>25</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -1214,16 +1211,16 @@
         <v>25</v>
       </c>
       <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -1231,19 +1228,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -1251,39 +1248,39 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="n">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -1291,19 +1288,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
@@ -1311,19 +1308,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -1331,39 +1328,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
         <v>26</v>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="n">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
       <c r="F43" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
@@ -1371,19 +1368,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
@@ -1391,19 +1388,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
         <v>5</v>
       </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" t="n">
-        <v>9</v>
-      </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
@@ -1411,19 +1408,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="n">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -1431,39 +1428,39 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" t="n">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -1474,16 +1471,16 @@
         <v>29</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
@@ -1494,19 +1491,19 @@
         <v>29</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -1514,16 +1511,16 @@
         <v>29</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
@@ -1534,16 +1531,16 @@
         <v>29</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F53" t="s">
         <v>9</v>
@@ -1554,16 +1551,16 @@
         <v>29</v>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
@@ -1574,16 +1571,16 @@
         <v>29</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
@@ -1591,19 +1588,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" t="s">
         <v>9</v>
@@ -1611,22 +1608,22 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -1634,16 +1631,16 @@
         <v>30</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
@@ -1654,16 +1651,16 @@
         <v>30</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
@@ -1674,16 +1671,16 @@
         <v>30</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F60" t="s">
         <v>9</v>
@@ -1694,16 +1691,16 @@
         <v>30</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F61" t="s">
         <v>9</v>
@@ -1714,16 +1711,16 @@
         <v>30</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -1734,16 +1731,16 @@
         <v>30</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
         <v>9</v>
@@ -1754,16 +1751,16 @@
         <v>30</v>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F64" t="s">
         <v>9</v>
@@ -1771,19 +1768,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" t="n">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -1794,13 +1791,13 @@
         <v>31</v>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -1814,16 +1811,16 @@
         <v>31</v>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -1834,16 +1831,16 @@
         <v>31</v>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -1854,16 +1851,16 @@
         <v>31</v>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -1874,13 +1871,13 @@
         <v>31</v>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -1894,13 +1891,13 @@
         <v>31</v>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -1914,16 +1911,16 @@
         <v>31</v>
       </c>
       <c r="B72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
@@ -1934,16 +1931,16 @@
         <v>31</v>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -1954,7 +1951,7 @@
         <v>32</v>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -1974,7 +1971,7 @@
         <v>32</v>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
@@ -1994,7 +1991,7 @@
         <v>32</v>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -2014,7 +2011,7 @@
         <v>32</v>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -2023,7 +2020,7 @@
         <v>4</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
@@ -2034,7 +2031,7 @@
         <v>32</v>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
@@ -2054,7 +2051,7 @@
         <v>32</v>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -2074,7 +2071,7 @@
         <v>32</v>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
@@ -2094,7 +2091,7 @@
         <v>32</v>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -2103,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -2111,19 +2108,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -2134,13 +2131,13 @@
         <v>33</v>
       </c>
       <c r="B83" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
         <v>10</v>
       </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -2154,13 +2151,13 @@
         <v>33</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -2174,13 +2171,13 @@
         <v>33</v>
       </c>
       <c r="B85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -2194,13 +2191,13 @@
         <v>33</v>
       </c>
       <c r="B86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -2214,13 +2211,13 @@
         <v>33</v>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -2234,13 +2231,13 @@
         <v>33</v>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -2254,13 +2251,13 @@
         <v>33</v>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -2271,16 +2268,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -2291,16 +2288,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" t="n">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
         <v>10</v>
       </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -2314,13 +2311,13 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -2334,16 +2331,16 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -2354,13 +2351,13 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -2374,13 +2371,13 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -2394,13 +2391,13 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -2414,258 +2411,18 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>34</v>
-      </c>
-      <c r="B98" t="n">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" t="n">
-        <v>7</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>34</v>
-      </c>
-      <c r="B99" t="n">
-        <v>11</v>
-      </c>
-      <c r="C99" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" t="n">
-        <v>8</v>
-      </c>
-      <c r="E99" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" t="n">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
-        <v>17</v>
-      </c>
-      <c r="D100" t="n">
-        <v>9</v>
-      </c>
-      <c r="E100" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>35</v>
-      </c>
-      <c r="B101" t="n">
-        <v>12</v>
-      </c>
-      <c r="C101" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B102" t="n">
-        <v>12</v>
-      </c>
-      <c r="C102" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>35</v>
-      </c>
-      <c r="B103" t="n">
-        <v>12</v>
-      </c>
-      <c r="C103" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3</v>
-      </c>
-      <c r="E103" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" t="n">
-        <v>12</v>
-      </c>
-      <c r="C104" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" t="s">
-        <v>19</v>
-      </c>
-      <c r="F104" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>35</v>
-      </c>
-      <c r="B105" t="n">
-        <v>12</v>
-      </c>
-      <c r="C105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>35</v>
-      </c>
-      <c r="B106" t="n">
-        <v>12</v>
-      </c>
-      <c r="C106" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" t="n">
-        <v>6</v>
-      </c>
-      <c r="E106" t="s">
-        <v>8</v>
-      </c>
-      <c r="F106" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>35</v>
-      </c>
-      <c r="B107" t="n">
-        <v>12</v>
-      </c>
-      <c r="C107" t="s">
-        <v>15</v>
-      </c>
-      <c r="D107" t="n">
-        <v>7</v>
-      </c>
-      <c r="E107" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>35</v>
-      </c>
-      <c r="B108" t="n">
-        <v>12</v>
-      </c>
-      <c r="C108" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" t="n">
-        <v>8</v>
-      </c>
-      <c r="E108" t="s">
-        <v>19</v>
-      </c>
-      <c r="F108" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>35</v>
-      </c>
-      <c r="B109" t="n">
-        <v>12</v>
-      </c>
-      <c r="C109" t="s">
-        <v>17</v>
-      </c>
-      <c r="D109" t="n">
-        <v>9</v>
-      </c>
-      <c r="E109" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2814,10 +2571,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -2854,24 +2611,24 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
         <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2882,16 +2639,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2902,16 +2659,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2922,16 +2679,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -2942,16 +2699,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2962,16 +2719,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2982,56 +2739,56 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -3042,16 +2799,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -3062,16 +2819,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -3082,179 +2839,179 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
-      </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -3262,56 +3019,56 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -3322,22 +3079,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
         <v>27</v>
-      </c>
-      <c r="F33" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -3345,19 +3102,19 @@
         <v>25</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -3365,13 +3122,13 @@
         <v>25</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -3385,19 +3142,19 @@
         <v>25</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -3405,33 +3162,33 @@
         <v>25</v>
       </c>
       <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -3442,79 +3199,79 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="n">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -3522,99 +3279,99 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" t="s">
         <v>27</v>
-      </c>
-      <c r="F45" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
         <v>5</v>
       </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" t="n">
-        <v>9</v>
-      </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="n">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -3622,42 +3379,42 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" t="n">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -3665,19 +3422,19 @@
         <v>29</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -3685,19 +3442,19 @@
         <v>29</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -3705,13 +3462,13 @@
         <v>29</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -3725,19 +3482,19 @@
         <v>29</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -3745,19 +3502,19 @@
         <v>29</v>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
@@ -3765,53 +3522,53 @@
         <v>29</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -3825,13 +3582,13 @@
         <v>30</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -3845,19 +3602,19 @@
         <v>30</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -3865,19 +3622,19 @@
         <v>30</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3885,13 +3642,13 @@
         <v>30</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -3905,19 +3662,19 @@
         <v>30</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -3925,13 +3682,13 @@
         <v>30</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3945,39 +3702,39 @@
         <v>30</v>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F64" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" t="n">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -3985,13 +3742,13 @@
         <v>31</v>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -4005,19 +3762,19 @@
         <v>31</v>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -4025,19 +3782,19 @@
         <v>31</v>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F68" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -4045,13 +3802,13 @@
         <v>31</v>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -4065,13 +3822,13 @@
         <v>31</v>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -4085,19 +3842,19 @@
         <v>31</v>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -4105,19 +3862,19 @@
         <v>31</v>
       </c>
       <c r="B72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -4125,13 +3882,13 @@
         <v>31</v>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -4145,7 +3902,7 @@
         <v>32</v>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -4165,7 +3922,7 @@
         <v>32</v>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
@@ -4185,7 +3942,7 @@
         <v>32</v>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -4194,10 +3951,10 @@
         <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
@@ -4205,7 +3962,7 @@
         <v>32</v>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -4225,7 +3982,7 @@
         <v>32</v>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
@@ -4245,7 +4002,7 @@
         <v>32</v>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -4265,7 +4022,7 @@
         <v>32</v>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
@@ -4274,10 +4031,10 @@
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -4285,7 +4042,7 @@
         <v>32</v>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -4302,16 +4059,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -4325,13 +4082,13 @@
         <v>33</v>
       </c>
       <c r="B83" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
         <v>10</v>
       </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -4345,13 +4102,13 @@
         <v>33</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -4365,13 +4122,13 @@
         <v>33</v>
       </c>
       <c r="B85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -4385,13 +4142,13 @@
         <v>33</v>
       </c>
       <c r="B86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -4405,13 +4162,13 @@
         <v>33</v>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -4425,13 +4182,13 @@
         <v>33</v>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -4445,13 +4202,13 @@
         <v>33</v>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -4462,16 +4219,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -4482,16 +4239,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" t="n">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
         <v>10</v>
       </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -4505,13 +4262,13 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -4525,13 +4282,13 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -4545,13 +4302,13 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -4565,13 +4322,13 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -4585,13 +4342,13 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -4605,258 +4362,18 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>34</v>
-      </c>
-      <c r="B98" t="n">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" t="n">
-        <v>7</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>34</v>
-      </c>
-      <c r="B99" t="n">
-        <v>11</v>
-      </c>
-      <c r="C99" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" t="n">
-        <v>8</v>
-      </c>
-      <c r="E99" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" t="n">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
-        <v>17</v>
-      </c>
-      <c r="D100" t="n">
-        <v>9</v>
-      </c>
-      <c r="E100" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>35</v>
-      </c>
-      <c r="B101" t="n">
-        <v>12</v>
-      </c>
-      <c r="C101" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B102" t="n">
-        <v>12</v>
-      </c>
-      <c r="C102" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>35</v>
-      </c>
-      <c r="B103" t="n">
-        <v>12</v>
-      </c>
-      <c r="C103" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3</v>
-      </c>
-      <c r="E103" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" t="n">
-        <v>12</v>
-      </c>
-      <c r="C104" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>35</v>
-      </c>
-      <c r="B105" t="n">
-        <v>12</v>
-      </c>
-      <c r="C105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>35</v>
-      </c>
-      <c r="B106" t="n">
-        <v>12</v>
-      </c>
-      <c r="C106" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" t="n">
-        <v>6</v>
-      </c>
-      <c r="E106" t="s">
-        <v>8</v>
-      </c>
-      <c r="F106" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>35</v>
-      </c>
-      <c r="B107" t="n">
-        <v>12</v>
-      </c>
-      <c r="C107" t="s">
-        <v>15</v>
-      </c>
-      <c r="D107" t="n">
-        <v>7</v>
-      </c>
-      <c r="E107" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>35</v>
-      </c>
-      <c r="B108" t="n">
-        <v>12</v>
-      </c>
-      <c r="C108" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" t="n">
-        <v>8</v>
-      </c>
-      <c r="E108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>35</v>
-      </c>
-      <c r="B109" t="n">
-        <v>12</v>
-      </c>
-      <c r="C109" t="s">
-        <v>17</v>
-      </c>
-      <c r="D109" t="n">
-        <v>9</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4905,10 +4422,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4925,10 +4442,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -4945,10 +4462,10 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -4965,10 +4482,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -5005,10 +4522,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -5025,10 +4542,10 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
         <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -5045,124 +4562,124 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -5173,362 +4690,362 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
-      </c>
       <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
         <v>27</v>
-      </c>
-      <c r="F19" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
-      </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -5536,19 +5053,19 @@
         <v>25</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -5556,19 +5073,19 @@
         <v>25</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
@@ -5576,19 +5093,19 @@
         <v>25</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -5596,259 +5113,259 @@
         <v>25</v>
       </c>
       <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="n">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
         <v>5</v>
       </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" t="n">
-        <v>9</v>
-      </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="n">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" t="n">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -5856,19 +5373,19 @@
         <v>29</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -5876,19 +5393,19 @@
         <v>29</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
@@ -5896,19 +5413,19 @@
         <v>29</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -5916,19 +5433,19 @@
         <v>29</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -5936,19 +5453,19 @@
         <v>29</v>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
         <v>39</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
@@ -5956,59 +5473,59 @@
         <v>29</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
@@ -6016,19 +5533,19 @@
         <v>30</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
@@ -6036,19 +5553,19 @@
         <v>30</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
         <v>47</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -6056,19 +5573,19 @@
         <v>30</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -6076,19 +5593,19 @@
         <v>30</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
@@ -6096,19 +5613,19 @@
         <v>30</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>39</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
@@ -6116,19 +5633,19 @@
         <v>30</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -6136,39 +5653,39 @@
         <v>30</v>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" t="n">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -6176,19 +5693,19 @@
         <v>31</v>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
@@ -6196,19 +5713,19 @@
         <v>31</v>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
@@ -6216,19 +5733,19 @@
         <v>31</v>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F68" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -6236,19 +5753,19 @@
         <v>31</v>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F69" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
@@ -6256,19 +5773,19 @@
         <v>31</v>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
@@ -6276,19 +5793,19 @@
         <v>31</v>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
@@ -6296,19 +5813,19 @@
         <v>31</v>
       </c>
       <c r="B72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -6316,19 +5833,19 @@
         <v>31</v>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F73" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -6336,7 +5853,7 @@
         <v>32</v>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -6345,10 +5862,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
@@ -6356,7 +5873,7 @@
         <v>32</v>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
@@ -6365,10 +5882,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76">
@@ -6376,7 +5893,7 @@
         <v>32</v>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -6385,10 +5902,10 @@
         <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
@@ -6396,7 +5913,7 @@
         <v>32</v>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -6405,10 +5922,10 @@
         <v>4</v>
       </c>
       <c r="E77" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F77" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -6416,7 +5933,7 @@
         <v>32</v>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
@@ -6425,10 +5942,10 @@
         <v>5</v>
       </c>
       <c r="E78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
@@ -6436,7 +5953,7 @@
         <v>32</v>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -6445,10 +5962,10 @@
         <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
@@ -6456,7 +5973,7 @@
         <v>32</v>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
@@ -6465,10 +5982,10 @@
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
@@ -6476,7 +5993,7 @@
         <v>32</v>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -6485,30 +6002,30 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -6516,19 +6033,19 @@
         <v>33</v>
       </c>
       <c r="B83" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
         <v>10</v>
       </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
@@ -6536,19 +6053,19 @@
         <v>33</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F84" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
@@ -6556,19 +6073,19 @@
         <v>33</v>
       </c>
       <c r="B85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -6576,19 +6093,19 @@
         <v>33</v>
       </c>
       <c r="B86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F86" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
@@ -6596,19 +6113,19 @@
         <v>33</v>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
@@ -6616,19 +6133,19 @@
         <v>33</v>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F88" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
@@ -6636,59 +6153,59 @@
         <v>33</v>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F89" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F90" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" t="n">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
         <v>10</v>
       </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F91" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
@@ -6696,19 +6213,19 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
@@ -6716,19 +6233,19 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94">
@@ -6736,19 +6253,19 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
@@ -6756,19 +6273,19 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
@@ -6776,19 +6293,19 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
@@ -6796,259 +6313,19 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F97" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>34</v>
-      </c>
-      <c r="B98" t="n">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" t="n">
-        <v>7</v>
-      </c>
-      <c r="E98" t="s">
-        <v>44</v>
-      </c>
-      <c r="F98" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>34</v>
-      </c>
-      <c r="B99" t="n">
-        <v>11</v>
-      </c>
-      <c r="C99" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" t="n">
-        <v>8</v>
-      </c>
-      <c r="E99" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" t="n">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
-        <v>17</v>
-      </c>
-      <c r="D100" t="n">
-        <v>9</v>
-      </c>
-      <c r="E100" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>35</v>
-      </c>
-      <c r="B101" t="n">
-        <v>12</v>
-      </c>
-      <c r="C101" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
-        <v>44</v>
-      </c>
-      <c r="F101" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B102" t="n">
-        <v>12</v>
-      </c>
-      <c r="C102" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="s">
-        <v>44</v>
-      </c>
-      <c r="F102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>35</v>
-      </c>
-      <c r="B103" t="n">
-        <v>12</v>
-      </c>
-      <c r="C103" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3</v>
-      </c>
-      <c r="E103" t="s">
-        <v>44</v>
-      </c>
-      <c r="F103" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" t="n">
-        <v>12</v>
-      </c>
-      <c r="C104" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>35</v>
-      </c>
-      <c r="B105" t="n">
-        <v>12</v>
-      </c>
-      <c r="C105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>35</v>
-      </c>
-      <c r="B106" t="n">
-        <v>12</v>
-      </c>
-      <c r="C106" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" t="n">
-        <v>6</v>
-      </c>
-      <c r="E106" t="s">
-        <v>47</v>
-      </c>
-      <c r="F106" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>35</v>
-      </c>
-      <c r="B107" t="n">
-        <v>12</v>
-      </c>
-      <c r="C107" t="s">
-        <v>15</v>
-      </c>
-      <c r="D107" t="n">
-        <v>7</v>
-      </c>
-      <c r="E107" t="s">
-        <v>42</v>
-      </c>
-      <c r="F107" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>35</v>
-      </c>
-      <c r="B108" t="n">
-        <v>12</v>
-      </c>
-      <c r="C108" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" t="n">
-        <v>8</v>
-      </c>
-      <c r="E108" t="s">
-        <v>47</v>
-      </c>
-      <c r="F108" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>35</v>
-      </c>
-      <c r="B109" t="n">
-        <v>12</v>
-      </c>
-      <c r="C109" t="s">
-        <v>17</v>
-      </c>
-      <c r="D109" t="n">
-        <v>9</v>
-      </c>
-      <c r="E109" t="s">
-        <v>44</v>
-      </c>
-      <c r="F109" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/figure_data/fig3.xlsx
+++ b/Outcome/Appendix/figure_data/fig3.xlsx
@@ -2271,7 +2271,7 @@
         <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -2291,7 +2291,7 @@
         <v>34</v>
       </c>
       <c r="B91" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
@@ -2311,7 +2311,7 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -2331,7 +2331,7 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -2351,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
@@ -2371,7 +2371,7 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -2391,7 +2391,7 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -2411,7 +2411,7 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -4222,7 +4222,7 @@
         <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -4242,7 +4242,7 @@
         <v>34</v>
       </c>
       <c r="B91" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
@@ -4262,7 +4262,7 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -4282,7 +4282,7 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -4302,7 +4302,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
@@ -4322,7 +4322,7 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -4342,7 +4342,7 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
@@ -6173,7 +6173,7 @@
         <v>34</v>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -6193,7 +6193,7 @@
         <v>34</v>
       </c>
       <c r="B91" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
@@ -6213,7 +6213,7 @@
         <v>34</v>
       </c>
       <c r="B92" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -6233,7 +6233,7 @@
         <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -6253,7 +6253,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
@@ -6273,7 +6273,7 @@
         <v>34</v>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -6293,7 +6293,7 @@
         <v>34</v>
       </c>
       <c r="B96" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -6313,7 +6313,7 @@
         <v>34</v>
       </c>
       <c r="B97" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C97" t="s">
         <v>16</v>
